--- a/data/raw_equipo/SOCs.xlsx
+++ b/data/raw_equipo/SOCs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\giovl\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos\old\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA484146-578B-4F16-998E-10B292BAA530}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A5316DA-10B6-4FCC-9D1E-34EB0C622F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="9" xr2:uid="{4357F51C-8BB4-4C65-8381-C1E9DA22FE88}"/>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="17280" windowHeight="8880" firstSheet="2" activeTab="2" xr2:uid="{4357F51C-8BB4-4C65-8381-C1E9DA22FE88}"/>
   </bookViews>
   <sheets>
     <sheet name="SOC 1" sheetId="11" r:id="rId1"/>
@@ -4479,6 +4479,10 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <f>E18/F18</f>
+        <v>2.616562333258496</v>
+      </c>
       <c r="F25" s="12"/>
     </row>
   </sheetData>
@@ -4551,7 +4555,7 @@
       </c>
       <c r="E3" s="81">
         <f>'SOC 2 ES'!J11</f>
-        <v>5.2783575033984036</v>
+        <v>1.7594525011328015</v>
       </c>
       <c r="F3" s="81">
         <f>'SOC 2 GUA'!G17</f>
@@ -4559,11 +4563,11 @@
       </c>
       <c r="G3" s="81">
         <f>'SOC 2 PAN'!I18</f>
-        <v>2.6187904441997403</v>
+        <v>0.87293014806658009</v>
       </c>
       <c r="H3" s="81">
         <f>AVERAGE(B3:G3)</f>
-        <v>3.8917968919184229</v>
+        <v>3.0143360088519628</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -4584,7 +4588,7 @@
       </c>
       <c r="E4" s="81">
         <f>'SOC 2 ES'!J12</f>
-        <v>5.1863096066683001</v>
+        <v>1.7287698688894335</v>
       </c>
       <c r="F4" s="81">
         <f>'SOC 2 GUA'!G18</f>
@@ -4592,11 +4596,11 @@
       </c>
       <c r="G4" s="81">
         <f>'SOC 2 PAN'!I19</f>
-        <v>2.3465016643817984</v>
+        <v>0.78216722146059947</v>
       </c>
       <c r="H4" s="81">
         <f t="shared" ref="H4:H7" si="0">AVERAGE(B4:G4)</f>
-        <v>3.9056776841130865</v>
+        <v>3.068698653996409</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -4617,7 +4621,7 @@
       </c>
       <c r="E5" s="81">
         <f>'SOC 2 ES'!J13</f>
-        <v>5.5950996912362472</v>
+        <v>1.865033230412082</v>
       </c>
       <c r="F5" s="81">
         <f>'SOC 2 GUA'!G19</f>
@@ -4625,11 +4629,11 @@
       </c>
       <c r="G5" s="81">
         <f>'SOC 2 PAN'!I20</f>
-        <v>2.4009842295206485</v>
+        <v>0.80032807650688276</v>
       </c>
       <c r="H5" s="81">
         <f t="shared" si="0"/>
-        <v>4.0740190221027399</v>
+        <v>3.1855652531297518</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -4650,7 +4654,7 @@
       </c>
       <c r="E6" s="81">
         <f>'SOC 2 ES'!J14</f>
-        <v>6.0934972216871826</v>
+        <v>2.0311657405623942</v>
       </c>
       <c r="F6" s="81">
         <f>'SOC 2 GUA'!G20</f>
@@ -4658,11 +4662,11 @@
       </c>
       <c r="G6" s="81">
         <f>'SOC 2 PAN'!I21</f>
-        <v>2.2521875708822363</v>
+        <v>0.7507291902940787</v>
       </c>
       <c r="H6" s="81">
         <f t="shared" si="0"/>
-        <v>4.0558104809329061</v>
+        <v>3.1285121706474146</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -4683,7 +4687,7 @@
       </c>
       <c r="E7" s="81">
         <f>'SOC 2 ES'!J15</f>
-        <v>6.1899267857021396</v>
+        <v>2.0633089285673574</v>
       </c>
       <c r="F7" s="81">
         <f>'SOC 2 GUA'!G21</f>
@@ -4691,11 +4695,11 @@
       </c>
       <c r="G7" s="81">
         <f>'SOC 2 PAN'!I22</f>
-        <v>2.4166226309468071</v>
+        <v>0.80554087698227039</v>
       </c>
       <c r="H7" s="81">
         <f t="shared" si="0"/>
-        <v>4.416709446457916</v>
+        <v>3.460426177941363</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -4754,7 +4758,7 @@
       </c>
       <c r="E12" s="81">
         <f>'SOC 2 ES'!K11</f>
-        <v>21.703610375540475</v>
+        <v>7.2345367918468257</v>
       </c>
       <c r="F12" s="81">
         <f>'SOC 2 GUA'!H17</f>
@@ -4762,11 +4766,11 @@
       </c>
       <c r="G12" s="81">
         <f>'SOC 2 PAN'!J18</f>
-        <v>33.155756674316351</v>
+        <v>11.051918891438783</v>
       </c>
       <c r="H12" s="81">
         <f>AVERAGE(B12:G12)</f>
-        <v>27.092981426593326</v>
+        <v>20.997496198831453</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -4787,7 +4791,7 @@
       </c>
       <c r="E13" s="81">
         <f>'SOC 2 ES'!K12</f>
-        <v>20.743556380314278</v>
+        <v>6.9145187934380932</v>
       </c>
       <c r="F13" s="81">
         <f>'SOC 2 GUA'!H18</f>
@@ -4795,11 +4799,11 @@
       </c>
       <c r="G13" s="81">
         <f>'SOC 2 PAN'!J19</f>
-        <v>26.871228891546135</v>
+        <v>8.957076297182045</v>
       </c>
       <c r="H13" s="81">
         <f t="shared" ref="H13:H16" si="1">AVERAGE(B13:G13)</f>
-        <v>25.173822669294086</v>
+        <v>19.88329097242071</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -4820,7 +4824,7 @@
       </c>
       <c r="E14" s="81">
         <f>'SOC 2 ES'!K13</f>
-        <v>21.026279414897996</v>
+        <v>7.0087598049659983</v>
       </c>
       <c r="F14" s="81">
         <f>'SOC 2 GUA'!H19</f>
@@ -4828,11 +4832,11 @@
       </c>
       <c r="G14" s="81">
         <f>'SOC 2 PAN'!J20</f>
-        <v>30.37673705619569</v>
+        <v>10.125579018731898</v>
       </c>
       <c r="H14" s="81">
         <f t="shared" si="1"/>
-        <v>25.453473946535414</v>
+        <v>19.742027671969453</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
@@ -4853,7 +4857,7 @@
       </c>
       <c r="E15" s="81">
         <f>'SOC 2 ES'!K14</f>
-        <v>22.663872328009997</v>
+        <v>7.5546241093366664</v>
       </c>
       <c r="F15" s="81">
         <f>'SOC 2 GUA'!H20</f>
@@ -4861,11 +4865,11 @@
       </c>
       <c r="G15" s="81">
         <f>'SOC 2 PAN'!J21</f>
-        <v>29.278437526530155</v>
+        <v>9.7594791755100516</v>
       </c>
       <c r="H15" s="81">
         <f t="shared" si="1"/>
-        <v>24.065601848359048</v>
+        <v>18.294234086743476</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
@@ -4886,7 +4890,7 @@
       </c>
       <c r="E16" s="81">
         <f>'SOC 2 ES'!K15</f>
-        <v>21.726500729732965</v>
+        <v>7.2421669099111003</v>
       </c>
       <c r="F16" s="81">
         <f>'SOC 2 GUA'!H21</f>
@@ -4894,11 +4898,11 @@
       </c>
       <c r="G16" s="81">
         <f>'SOC 2 PAN'!J22</f>
-        <v>31.404905131811624</v>
+        <v>10.468301710603896</v>
       </c>
       <c r="H16" s="81">
         <f t="shared" si="1"/>
-        <v>25.492176921123612</v>
+        <v>19.588687380952013</v>
       </c>
     </row>
   </sheetData>
@@ -5706,6 +5710,10 @@
       <c r="F27" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C29">
+        <f>C21/D21</f>
+        <v>7.4103893519430883</v>
+      </c>
       <c r="D29" s="27"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
@@ -5731,7 +5739,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{937ACA9C-5A24-424A-9E03-13B84A52246F}">
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="17.33203125" customWidth="1"/>
@@ -6114,6 +6122,12 @@
         <v>159890.68020351915</v>
       </c>
     </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="D10">
+        <f>D7/D3</f>
+        <v>20.637541035932827</v>
+      </c>
+    </row>
     <row r="12" spans="1:17" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>27</v>
@@ -6253,6 +6267,12 @@
       <c r="F17" s="77">
         <f>(B17/D17)*100</f>
         <v>49.082692575959328</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C19">
+        <f>C13/D13</f>
+        <v>11.217169058449294</v>
       </c>
     </row>
   </sheetData>
@@ -6267,7 +6287,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBC77F80-00A9-4B63-AE12-0C0F77D881C3}">
-  <dimension ref="A2:K17"/>
+  <dimension ref="A2:K21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="19.6640625" customWidth="1"/>
@@ -6311,35 +6331,35 @@
       </c>
       <c r="B3" s="88">
         <f>_xlfn.FORECAST.LINEAR(A3,B4:B7,A4:A7)</f>
-        <v>78.305000000000291</v>
+        <v>234.91499999999724</v>
       </c>
       <c r="C3" s="88">
         <f>_xlfn.FORECAST.LINEAR(A3,C4:C7,A4:A7)</f>
-        <v>139.90499999999884</v>
+        <v>419.71499999999651</v>
       </c>
       <c r="D3" s="1">
         <f>_xlfn.FORECAST.LINEAR(A3,D4:D7,A4:A7)</f>
-        <v>194.59000000000378</v>
+        <v>583.76999999998952</v>
       </c>
       <c r="E3" s="1">
         <f>_xlfn.FORECAST.LINEAR(A3,E4:E7,A4:A7)</f>
-        <v>269.02000000000407</v>
+        <v>807.06000000002678</v>
       </c>
       <c r="F3" s="1">
         <f>_xlfn.FORECAST.LINEAR(A3,F4:F7,A4:A7)</f>
-        <v>495.8799999999901</v>
+        <v>1487.640000000014</v>
       </c>
       <c r="G3" s="87">
         <f>AVERAGE(C3:F3)</f>
-        <v>274.8487499999992</v>
+        <v>824.54625000000669</v>
       </c>
       <c r="H3" s="1">
         <f>G3*12</f>
-        <v>3298.1849999999904</v>
+        <v>9894.5550000000803</v>
       </c>
       <c r="I3" s="1">
         <f>B3*12</f>
-        <v>939.66000000000349</v>
+        <v>2818.9799999999668</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
@@ -6347,31 +6367,36 @@
         <v>2021</v>
       </c>
       <c r="B4" s="89">
-        <v>81.25</v>
+        <f>81.25*3</f>
+        <v>243.75</v>
       </c>
       <c r="C4" s="89">
-        <v>147.69999999999999</v>
+        <f>147.7*3</f>
+        <v>443.09999999999997</v>
       </c>
       <c r="D4" s="89">
-        <v>208.23</v>
+        <f>208.23*3</f>
+        <v>624.68999999999994</v>
       </c>
       <c r="E4" s="89">
-        <v>291.24</v>
+        <f>291.24*3</f>
+        <v>873.72</v>
       </c>
       <c r="F4" s="89">
-        <v>561.62</v>
+        <f>561.62*3</f>
+        <v>1684.8600000000001</v>
       </c>
       <c r="G4" s="87">
         <f t="shared" ref="G4:G7" si="0">AVERAGE(C4:F4)</f>
-        <v>302.19749999999999</v>
+        <v>906.59249999999997</v>
       </c>
       <c r="H4" s="89">
         <f>G4*12</f>
-        <v>3626.37</v>
+        <v>10879.11</v>
       </c>
       <c r="I4" s="89">
         <f>B4*12</f>
-        <v>975</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -6379,31 +6404,36 @@
         <v>2022</v>
       </c>
       <c r="B5" s="89">
-        <v>86.14</v>
+        <f>86.14*3</f>
+        <v>258.42</v>
       </c>
       <c r="C5" s="89">
-        <v>159.65</v>
+        <f>159.65*3</f>
+        <v>478.95000000000005</v>
       </c>
       <c r="D5" s="89">
-        <v>224.06</v>
+        <f>224.06*3</f>
+        <v>672.18000000000006</v>
       </c>
       <c r="E5" s="89">
-        <v>316.10000000000002</v>
+        <f>316.1*3</f>
+        <v>948.30000000000007</v>
       </c>
       <c r="F5" s="89">
-        <v>595.04</v>
+        <f>595.04*3</f>
+        <v>1785.12</v>
       </c>
       <c r="G5" s="87">
         <f t="shared" si="0"/>
-        <v>323.71249999999998</v>
+        <v>971.13750000000005</v>
       </c>
       <c r="H5" s="89">
         <f t="shared" ref="H5:H7" si="1">G5*12</f>
-        <v>3884.5499999999997</v>
+        <v>11653.650000000001</v>
       </c>
       <c r="I5" s="89">
         <f t="shared" ref="I5:I7" si="2">B5*12</f>
-        <v>1033.68</v>
+        <v>3101.04</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -6411,31 +6441,36 @@
         <v>2023</v>
       </c>
       <c r="B6" s="89">
-        <v>92.5</v>
+        <f>92.5*3</f>
+        <v>277.5</v>
       </c>
       <c r="C6" s="89">
-        <v>171.79</v>
+        <f>171.79*3</f>
+        <v>515.37</v>
       </c>
       <c r="D6" s="89">
-        <v>248.72</v>
+        <f>248.72*3</f>
+        <v>746.16</v>
       </c>
       <c r="E6" s="89">
-        <v>357.01</v>
+        <f>357.01*3</f>
+        <v>1071.03</v>
       </c>
       <c r="F6" s="89">
-        <v>702.36</v>
+        <f>702.36*3</f>
+        <v>2107.08</v>
       </c>
       <c r="G6" s="87">
         <f t="shared" si="0"/>
-        <v>369.97</v>
+        <v>1109.9099999999999</v>
       </c>
       <c r="H6" s="89">
         <f t="shared" si="1"/>
-        <v>4439.6400000000003</v>
+        <v>13318.919999999998</v>
       </c>
       <c r="I6" s="89">
         <f t="shared" si="2"/>
-        <v>1110</v>
+        <v>3330</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -6443,31 +6478,36 @@
         <v>2024</v>
       </c>
       <c r="B7" s="89">
-        <v>92.03</v>
+        <f>92.03*3</f>
+        <v>276.09000000000003</v>
       </c>
       <c r="C7" s="89">
-        <v>175.24</v>
+        <f>175.24*3</f>
+        <v>525.72</v>
       </c>
       <c r="D7" s="89">
-        <v>251.34</v>
+        <f>251.34*3</f>
+        <v>754.02</v>
       </c>
       <c r="E7" s="89">
-        <v>360.54</v>
+        <f>360.54*3</f>
+        <v>1081.6200000000001</v>
       </c>
       <c r="F7" s="89">
-        <v>726.52</v>
+        <f>726.52*3</f>
+        <v>2179.56</v>
       </c>
       <c r="G7" s="87">
         <f t="shared" si="0"/>
-        <v>378.41</v>
+        <v>1135.23</v>
       </c>
       <c r="H7" s="89">
         <f t="shared" si="1"/>
-        <v>4540.92</v>
+        <v>13622.76</v>
       </c>
       <c r="I7" s="89">
         <f t="shared" si="2"/>
-        <v>1104.3600000000001</v>
+        <v>3313.0800000000004</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
@@ -6525,19 +6565,19 @@
       </c>
       <c r="H11" s="1">
         <f>H7</f>
-        <v>4540.92</v>
+        <v>13622.76</v>
       </c>
       <c r="I11" s="1">
         <f>I7</f>
-        <v>1104.3600000000001</v>
+        <v>3313.0800000000004</v>
       </c>
       <c r="J11" s="1">
         <f>(G11/H11)*100</f>
-        <v>5.2783575033984036</v>
+        <v>1.7594525011328015</v>
       </c>
       <c r="K11" s="1">
         <f>(G11/I11)*100</f>
-        <v>21.703610375540475</v>
+        <v>7.2345367918468257</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -6563,19 +6603,19 @@
       </c>
       <c r="H12" s="1">
         <f>H6</f>
-        <v>4439.6400000000003</v>
+        <v>13318.919999999998</v>
       </c>
       <c r="I12" s="1">
         <f>I6</f>
-        <v>1110</v>
+        <v>3330</v>
       </c>
       <c r="J12" s="1">
         <f t="shared" ref="J12:J15" si="5">(G12/H12)*100</f>
-        <v>5.1863096066683001</v>
+        <v>1.7287698688894335</v>
       </c>
       <c r="K12" s="1">
         <f t="shared" ref="K12:K15" si="6">(G12/I12)*100</f>
-        <v>20.743556380314278</v>
+        <v>6.9145187934380932</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -6601,19 +6641,19 @@
       </c>
       <c r="H13" s="1">
         <f>H5</f>
-        <v>3884.5499999999997</v>
+        <v>11653.650000000001</v>
       </c>
       <c r="I13" s="1">
         <f>I5</f>
-        <v>1033.68</v>
+        <v>3101.04</v>
       </c>
       <c r="J13" s="1">
         <f t="shared" si="5"/>
-        <v>5.5950996912362472</v>
+        <v>1.865033230412082</v>
       </c>
       <c r="K13" s="1">
         <f t="shared" si="6"/>
-        <v>21.026279414897996</v>
+        <v>7.0087598049659983</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -6639,19 +6679,19 @@
       </c>
       <c r="H14" s="1">
         <f>H4</f>
-        <v>3626.37</v>
+        <v>10879.11</v>
       </c>
       <c r="I14" s="1">
         <f>I4</f>
-        <v>975</v>
+        <v>2925</v>
       </c>
       <c r="J14" s="1">
         <f t="shared" si="5"/>
-        <v>6.0934972216871826</v>
+        <v>2.0311657405623942</v>
       </c>
       <c r="K14" s="1">
         <f t="shared" si="6"/>
-        <v>22.663872328009997</v>
+        <v>7.5546241093366664</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -6677,19 +6717,19 @@
       </c>
       <c r="H15" s="1">
         <f>H3</f>
-        <v>3298.1849999999904</v>
+        <v>9894.5550000000803</v>
       </c>
       <c r="I15" s="1">
         <f>I3</f>
-        <v>939.66000000000349</v>
+        <v>2818.9799999999668</v>
       </c>
       <c r="J15" s="1">
         <f t="shared" si="5"/>
-        <v>6.1899267857021396</v>
+        <v>2.0633089285673574</v>
       </c>
       <c r="K15" s="1">
         <f t="shared" si="6"/>
-        <v>21.726500729732965</v>
+        <v>7.2421669099111003</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -6743,6 +6783,12 @@
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="D21">
+        <f>H11/I11</f>
+        <v>4.1118113658589586</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6753,7 +6799,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{16B654FD-2614-48E4-8B3C-4303E8A4258D}">
-  <dimension ref="A1:Q21"/>
+  <dimension ref="A1:Q24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.6640625" customWidth="1"/>
@@ -7376,6 +7422,12 @@
         <v>6.2259592177008898</v>
       </c>
     </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E24">
+        <f>E17/F17</f>
+        <v>3.7176560183095875</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
@@ -7387,7 +7439,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E486345-E526-4AA0-932C-5491DD4C5132}">
-  <dimension ref="A2:K22"/>
+  <dimension ref="A2:K25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="17.21875" bestFit="1" customWidth="1"/>
@@ -7603,32 +7655,32 @@
         <v>2024</v>
       </c>
       <c r="C10" s="81">
-        <f>B3+C3/2</f>
-        <v>145.04000370502473</v>
+        <f>(B3+C3/2)*3</f>
+        <v>435.12001111507419</v>
       </c>
       <c r="D10" s="81">
-        <f>E3+F3/2</f>
-        <v>652.67999505996704</v>
+        <f>(E3+F3/2)*3</f>
+        <v>1958.0399851799011</v>
       </c>
       <c r="E10" s="81">
-        <f t="shared" ref="E10:F13" si="0">G3+H3/2</f>
-        <v>1196.580019760132</v>
+        <f t="shared" ref="E10:F13" si="0">(G3+H3/2)*3</f>
+        <v>3589.7400592803961</v>
       </c>
       <c r="F10" s="81">
         <f t="shared" si="0"/>
-        <v>1595.4400098800661</v>
+        <v>4786.3200296401983</v>
       </c>
       <c r="G10" s="81">
-        <f>J3+K3/2</f>
-        <v>3900.5399604797367</v>
+        <f>(J3+K3/2)*3</f>
+        <v>11701.61988143921</v>
       </c>
       <c r="H10" s="1">
         <f>(AVERAGE(D10:G10))*12</f>
-        <v>22035.719955539706</v>
+        <v>66107.159866619113</v>
       </c>
       <c r="I10" s="1">
         <f>C10*12</f>
-        <v>1740.4800444602968</v>
+        <v>5221.4401333808901</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -7636,32 +7688,32 @@
         <v>2023</v>
       </c>
       <c r="C11" s="81">
-        <f>B4+C4/2</f>
-        <v>160.58000123500824</v>
+        <f>(B4+C4/2)*3</f>
+        <v>481.74000370502472</v>
       </c>
       <c r="D11" s="81">
-        <f>E4+F4/2</f>
-        <v>688.94000988006587</v>
+        <f>(E4+F4/2)*3</f>
+        <v>2066.8200296401974</v>
       </c>
       <c r="E11" s="81">
         <f t="shared" si="0"/>
-        <v>1201.7599901199342</v>
+        <v>3605.2799703598025</v>
       </c>
       <c r="F11" s="81">
         <f t="shared" si="0"/>
-        <v>1600.6199802398683</v>
+        <v>4801.8599407196052</v>
       </c>
       <c r="G11" s="81">
-        <f>J4+K4/2</f>
-        <v>3864.2801185607914</v>
+        <f>(J4+K4/2)*3</f>
+        <v>11592.840355682374</v>
       </c>
       <c r="H11" s="1">
-        <f t="shared" ref="H11:H14" si="1">(AVERAGE(D11:G11))*12</f>
-        <v>22066.80029640198</v>
+        <f t="shared" ref="H11:H13" si="1">(AVERAGE(D11:G11))*12</f>
+        <v>66200.400889205936</v>
       </c>
       <c r="I11" s="1">
         <f t="shared" ref="I11:I14" si="2">C11*12</f>
-        <v>1926.9600148200989</v>
+        <v>5780.8800444602966</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -7669,32 +7721,32 @@
         <v>2022</v>
       </c>
       <c r="C12" s="81">
-        <f>B5+C5/2</f>
-        <v>145.04000370502473</v>
+        <f>(B5+C5/2)*3</f>
+        <v>435.12001111507419</v>
       </c>
       <c r="D12" s="81">
-        <f>E5+F5/2</f>
-        <v>668.22000494003305</v>
+        <f>(E5+F5/2)*3</f>
+        <v>2004.6600148200991</v>
       </c>
       <c r="E12" s="81">
         <f t="shared" si="0"/>
-        <v>1181.040009880066</v>
+        <v>3543.120029640198</v>
       </c>
       <c r="F12" s="81">
         <f t="shared" si="0"/>
-        <v>1590.2599901199337</v>
+        <v>4770.7799703598012</v>
       </c>
       <c r="G12" s="81">
-        <f>J5+K5/2</f>
-        <v>3900.5399604797362</v>
+        <f>(J5+K5/2)*3</f>
+        <v>11701.619881439208</v>
       </c>
       <c r="H12" s="1">
         <f t="shared" si="1"/>
-        <v>22020.179896259306</v>
+        <v>66060.539688777921</v>
       </c>
       <c r="I12" s="1">
         <f t="shared" si="2"/>
-        <v>1740.4800444602968</v>
+        <v>5221.4401333808901</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -7702,32 +7754,32 @@
         <v>2021</v>
       </c>
       <c r="C13" s="81">
-        <f>B6+C6/2</f>
-        <v>139.86000247001647</v>
+        <f>(B6+C6/2)*3</f>
+        <v>419.5800074100494</v>
       </c>
       <c r="D13" s="81">
-        <f>E6+F6/2</f>
-        <v>600.87999505996709</v>
+        <f>(E6+F6/2)*3</f>
+        <v>1802.6399851799013</v>
       </c>
       <c r="E13" s="81">
         <f t="shared" si="0"/>
-        <v>1098.159990119934</v>
+        <v>3294.4799703598019</v>
       </c>
       <c r="F13" s="81">
         <f t="shared" si="0"/>
-        <v>1528.1</v>
+        <v>4584.2999999999993</v>
       </c>
       <c r="G13" s="81">
-        <f>J6+K6/2</f>
-        <v>4045.5799209594725</v>
+        <f>(J6+K6/2)*3</f>
+        <v>12136.739762878417</v>
       </c>
       <c r="H13" s="1">
         <f t="shared" si="1"/>
-        <v>21818.159718418119</v>
+        <v>65454.479155254361</v>
       </c>
       <c r="I13" s="1">
         <f t="shared" si="2"/>
-        <v>1678.3200296401976</v>
+        <v>5034.9600889205931</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -7735,32 +7787,32 @@
         <v>2020</v>
       </c>
       <c r="C14" s="81">
-        <f>_xlfn.FORECAST.LINEAR(B14,C10:C13,B10:B13)</f>
-        <v>139.8600024700163</v>
+        <f>(_xlfn.FORECAST.LINEAR(B14,C10:C13,B10:B13))</f>
+        <v>419.58000741004798</v>
       </c>
       <c r="D14" s="81">
-        <f>_xlfn.FORECAST.LINEAR(B14,D10:D13,B10:B13)</f>
-        <v>608.65000000000146</v>
+        <f>(_xlfn.FORECAST.LINEAR(B14,D10:D13,B10:B13))</f>
+        <v>1825.9499999999971</v>
       </c>
       <c r="E14" s="81">
-        <f>_xlfn.FORECAST.LINEAR(B14,E10:E13,B10:B13)</f>
-        <v>1090.3899851798997</v>
+        <f>(_xlfn.FORECAST.LINEAR(B14,E10:E13,B10:B13))</f>
+        <v>3271.1699555396917</v>
       </c>
       <c r="F14" s="81">
-        <f>_xlfn.FORECAST.LINEAR(B14,F10:F13,B10:B13)</f>
-        <v>1525.5099901199355</v>
+        <f>(_xlfn.FORECAST.LINEAR(B14,F10:F13,B10:B13))</f>
+        <v>4576.5299703597993</v>
       </c>
       <c r="G14" s="81">
-        <f>_xlfn.FORECAST.LINEAR(B14,G10:G13,B10:B13)</f>
-        <v>4045.5799209594697</v>
+        <f>(_xlfn.FORECAST.LINEAR(B14,G10:G13,B10:B13))</f>
+        <v>12136.739762878395</v>
       </c>
       <c r="H14" s="1">
-        <f t="shared" si="1"/>
-        <v>21810.389688777919</v>
+        <f>(AVERAGE(D14:G14))*12</f>
+        <v>65431.169066333649</v>
       </c>
       <c r="I14" s="1">
         <f t="shared" si="2"/>
-        <v>1678.3200296401956</v>
+        <v>5034.9600889205758</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
@@ -7818,19 +7870,19 @@
       </c>
       <c r="G18" s="1">
         <f t="shared" ref="G18:H22" si="3">H10</f>
-        <v>22035.719955539706</v>
+        <v>66107.159866619113</v>
       </c>
       <c r="H18" s="1">
         <f t="shared" si="3"/>
-        <v>1740.4800444602968</v>
+        <v>5221.4401333808901</v>
       </c>
       <c r="I18" s="81">
         <f>(F18/G18)*100</f>
-        <v>2.6187904441997403</v>
+        <v>0.87293014806658009</v>
       </c>
       <c r="J18" s="81">
         <f>(F18/H18)*100</f>
-        <v>33.155756674316351</v>
+        <v>11.051918891438783</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
@@ -7856,19 +7908,19 @@
       </c>
       <c r="G19" s="1">
         <f t="shared" si="3"/>
-        <v>22066.80029640198</v>
+        <v>66200.400889205936</v>
       </c>
       <c r="H19" s="1">
         <f t="shared" si="3"/>
-        <v>1926.9600148200989</v>
+        <v>5780.8800444602966</v>
       </c>
       <c r="I19" s="81">
         <f t="shared" ref="I19:I22" si="6">(F19/G19)*100</f>
-        <v>2.3465016643817984</v>
+        <v>0.78216722146059947</v>
       </c>
       <c r="J19" s="81">
         <f t="shared" ref="J19:J22" si="7">(F19/H19)*100</f>
-        <v>26.871228891546135</v>
+        <v>8.957076297182045</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
@@ -7894,19 +7946,19 @@
       </c>
       <c r="G20" s="1">
         <f t="shared" si="3"/>
-        <v>22020.179896259306</v>
+        <v>66060.539688777921</v>
       </c>
       <c r="H20" s="1">
         <f t="shared" si="3"/>
-        <v>1740.4800444602968</v>
+        <v>5221.4401333808901</v>
       </c>
       <c r="I20" s="81">
         <f t="shared" si="6"/>
-        <v>2.4009842295206485</v>
+        <v>0.80032807650688276</v>
       </c>
       <c r="J20" s="81">
         <f t="shared" si="7"/>
-        <v>30.37673705619569</v>
+        <v>10.125579018731898</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
@@ -7932,19 +7984,19 @@
       </c>
       <c r="G21" s="1">
         <f t="shared" si="3"/>
-        <v>21818.159718418119</v>
+        <v>65454.479155254361</v>
       </c>
       <c r="H21" s="1">
         <f t="shared" si="3"/>
-        <v>1678.3200296401976</v>
+        <v>5034.9600889205931</v>
       </c>
       <c r="I21" s="81">
         <f t="shared" si="6"/>
-        <v>2.2521875708822363</v>
+        <v>0.7507291902940787</v>
       </c>
       <c r="J21" s="81">
         <f t="shared" si="7"/>
-        <v>29.278437526530155</v>
+        <v>9.7594791755100516</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
@@ -7972,19 +8024,25 @@
       </c>
       <c r="G22" s="1">
         <f t="shared" si="3"/>
-        <v>21810.389688777919</v>
+        <v>65431.169066333649</v>
       </c>
       <c r="H22" s="1">
         <f t="shared" si="3"/>
-        <v>1678.3200296401956</v>
+        <v>5034.9600889205758</v>
       </c>
       <c r="I22" s="81">
         <f t="shared" si="6"/>
-        <v>2.4166226309468071</v>
+        <v>0.80554087698227039</v>
       </c>
       <c r="J22" s="81">
         <f t="shared" si="7"/>
-        <v>31.404905131811624</v>
+        <v>10.468301710603896</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E25">
+        <f>G18/H18</f>
+        <v>12.660713936753428</v>
       </c>
     </row>
   </sheetData>
